--- a/Investigadores y Hojas de Vida/Equipo.xlsx
+++ b/Investigadores y Hojas de Vida/Equipo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unbosqueeduco-my.sharepoint.com/personal/jleongomez_unbosque_edu_co/Documents/Research/Proyecto IDS/Investigadores y Hojas de Vida/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanl\GitHub\Proyecto-IDS\Investigadores y Hojas de Vida\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="11_F25DC773A252ABDACC1048AEA11E47925BDE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00F4B6A6-BAD2-40C3-9478-B56E6306CCE2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CF77DB-34D3-41DD-95EC-DDCAD3FC28CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
